--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential BSE Sensex Index Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential BSE Sensex Index Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="115">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential BSE Sensex Index Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -112,19 +112,25 @@
     <t>Construction</t>
   </si>
   <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
     <t>Tata Consultancy Services Ltd.</t>
   </si>
   <si>
     <t>INE467B01029</t>
   </si>
   <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
   </si>
   <si>
     <t>State Bank Of India</t>
@@ -133,12 +139,6 @@
     <t>INE062A01020</t>
   </si>
   <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
     <t>Kotak Mahindra Bank Ltd.</t>
   </si>
   <si>
@@ -154,21 +154,21 @@
     <t>Automobiles</t>
   </si>
   <si>
+    <t>Bajaj Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE296A01024</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
     <t>Hindustan Unilever Ltd.</t>
   </si>
   <si>
     <t>INE030A01027</t>
   </si>
   <si>
-    <t>Bajaj Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE296A01024</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
     <t>Sun Pharmaceutical Industries Ltd.</t>
   </si>
   <si>
@@ -184,6 +184,15 @@
     <t>INE860A01027</t>
   </si>
   <si>
+    <t>Zomato Ltd.</t>
+  </si>
+  <si>
+    <t>INE758T01015</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
     <t>Maruti Suzuki India Ltd.</t>
   </si>
   <si>
@@ -205,15 +214,6 @@
     <t>INE155A01022</t>
   </si>
   <si>
-    <t>Zomato Ltd.</t>
-  </si>
-  <si>
-    <t>INE758T01015</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
     <t>Titan Company Ltd.</t>
   </si>
   <si>
@@ -223,6 +223,15 @@
     <t>Consumer Durables</t>
   </si>
   <si>
+    <t>Tata Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
     <t>Power Grid Corporation Of India Ltd.</t>
   </si>
   <si>
@@ -238,13 +247,25 @@
     <t>Cement &amp; Cement Products</t>
   </si>
   <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
+    <t>Bajaj Finserv Ltd.</t>
+  </si>
+  <si>
+    <t>INE918I01026</t>
+  </si>
+  <si>
+    <t>Adani Ports and Special Economic Zone Ltd.</t>
+  </si>
+  <si>
+    <t>INE742F01042</t>
+  </si>
+  <si>
+    <t>Transport Infrastructure</t>
+  </si>
+  <si>
+    <t>Asian Paints Ltd.</t>
+  </si>
+  <si>
+    <t>INE021A01026</t>
   </si>
   <si>
     <t>Tech Mahindra Ltd.</t>
@@ -253,18 +274,6 @@
     <t>INE669C01036</t>
   </si>
   <si>
-    <t>Asian Paints Ltd.</t>
-  </si>
-  <si>
-    <t>INE021A01026</t>
-  </si>
-  <si>
-    <t>Bajaj Finserv Ltd.</t>
-  </si>
-  <si>
-    <t>INE918I01026</t>
-  </si>
-  <si>
     <t>Nestle India Ltd.</t>
   </si>
   <si>
@@ -274,30 +283,12 @@
     <t>Food Products</t>
   </si>
   <si>
-    <t>Adani Ports and Special Economic Zone Ltd.</t>
-  </si>
-  <si>
-    <t>INE742F01042</t>
-  </si>
-  <si>
-    <t>Transport Infrastructure</t>
-  </si>
-  <si>
     <t>IndusInd Bank Ltd.</t>
   </si>
   <si>
     <t>INE095A01012</t>
   </si>
   <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -355,7 +346,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -367,7 +358,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - BSE SENSEX TRI</t>
+    <t>Benchmark name - S&amp;P BSE SENSEX TRI</t>
   </si>
 </sst>
 </file>
@@ -738,13 +729,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -762,7 +753,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="15887700"/>
+          <a:off x="666750" y="15697200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -777,13 +768,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>106</xdr:row>
+      <xdr:row>105</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -801,7 +792,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="18745200"/>
+          <a:off x="666750" y="18554700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1135,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J95"/>
+  <dimension ref="B1:J94"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1235,10 +1226,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>175054.57</v>
+        <v>186574.59</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9993892494365998</v>
+        <v>0.9984950952484003</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1272,10 +1263,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>175054.57</v>
+        <v>186574.59</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9993892494365998</v>
+        <v>0.9984950952484003</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1298,13 +1289,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>1470399</v>
+        <v>1496702</v>
       </c>
       <c r="G8" s="15">
-        <v>24985.76</v>
+        <v>29104.87</v>
       </c>
       <c r="H8" s="16">
-        <v>0.1426440905429</v>
+        <v>0.1557611352268</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1327,13 +1318,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>1371032</v>
+        <v>1406435</v>
       </c>
       <c r="G9" s="15">
-        <v>17172.86</v>
+        <v>20336.35</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0980401235232</v>
+        <v>0.1088344652414</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1356,13 +1347,13 @@
         <v>22</v>
       </c>
       <c r="F10" s="14">
-        <v>1314874</v>
+        <v>1337035</v>
       </c>
       <c r="G10" s="15">
-        <v>16631.84</v>
+        <v>18996.59</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0949514319698</v>
+        <v>0.1016644439174</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1385,13 +1376,13 @@
         <v>25</v>
       </c>
       <c r="F11" s="14">
-        <v>701983</v>
+        <v>705638</v>
       </c>
       <c r="G11" s="15">
-        <v>13197.63</v>
+        <v>11027.71</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0753454739288</v>
+        <v>0.0590172238719</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1414,13 +1405,13 @@
         <v>28</v>
       </c>
       <c r="F12" s="14">
-        <v>520082</v>
+        <v>529572</v>
       </c>
       <c r="G12" s="15">
-        <v>8460.43</v>
+        <v>9833.09</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0483007258115</v>
+        <v>0.0526239512902</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1443,13 +1434,13 @@
         <v>31</v>
       </c>
       <c r="F13" s="14">
-        <v>227106</v>
+        <v>230974</v>
       </c>
       <c r="G13" s="15">
-        <v>8101.33</v>
+        <v>8490.03</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0462506183537</v>
+        <v>0.0454362692879</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1469,16 +1460,16 @@
         <v>13</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F14" s="14">
-        <v>196851</v>
+        <v>1829676</v>
       </c>
       <c r="G14" s="15">
-        <v>8088.61</v>
+        <v>7646.22</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0461779996768</v>
+        <v>0.0409204338447</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1489,25 +1480,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F15" s="14">
-        <v>1798951</v>
+        <v>200181</v>
       </c>
       <c r="G15" s="15">
-        <v>8051.21</v>
+        <v>6935.27</v>
       </c>
       <c r="H15" s="16">
-        <v>0.045964482498</v>
+        <v>0.0371156280136</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1530,13 +1521,13 @@
         <v>17</v>
       </c>
       <c r="F16" s="14">
-        <v>745752</v>
+        <v>562895</v>
       </c>
       <c r="G16" s="15">
-        <v>5765.41</v>
+        <v>6709.99</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0329148149208</v>
+        <v>0.0359099923745</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1559,13 +1550,13 @@
         <v>17</v>
       </c>
       <c r="F17" s="14">
-        <v>553200</v>
+        <v>758326</v>
       </c>
       <c r="G17" s="15">
-        <v>5456.76</v>
+        <v>6160.64</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0311527272939</v>
+        <v>0.0329700246083</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1588,13 +1579,13 @@
         <v>17</v>
       </c>
       <c r="F18" s="14">
-        <v>285886</v>
+        <v>290723</v>
       </c>
       <c r="G18" s="15">
-        <v>5439.41</v>
+        <v>6034.54</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0310536758753</v>
+        <v>0.0322951726282</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1617,13 +1608,13 @@
         <v>45</v>
       </c>
       <c r="F19" s="14">
-        <v>171559</v>
+        <v>174460</v>
       </c>
       <c r="G19" s="15">
-        <v>5132.44</v>
+        <v>5196.20</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0293011793944</v>
+        <v>0.0278086110972</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1643,16 +1634,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F20" s="14">
-        <v>173490</v>
+        <v>51441</v>
       </c>
       <c r="G20" s="15">
-        <v>4287.46</v>
+        <v>4719.58</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0244771754967</v>
+        <v>0.0252578739775</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1663,25 +1654,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="F21" s="14">
-        <v>54115</v>
+        <v>176426</v>
       </c>
       <c r="G21" s="15">
-        <v>4267.27</v>
+        <v>4144.86</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0243619104742</v>
+        <v>0.0221821330573</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1704,13 +1695,13 @@
         <v>53</v>
       </c>
       <c r="F22" s="14">
-        <v>209799</v>
+        <v>213344</v>
       </c>
       <c r="G22" s="15">
-        <v>3657.01</v>
+        <v>3580.55</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0208779266893</v>
+        <v>0.0191621035495</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1733,13 +1724,13 @@
         <v>25</v>
       </c>
       <c r="F23" s="14">
-        <v>205647</v>
+        <v>209127</v>
       </c>
       <c r="G23" s="15">
-        <v>3547.82</v>
+        <v>3424.56</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0202545592893</v>
+        <v>0.0183272886376</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1759,16 +1750,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F24" s="14">
-        <v>25644</v>
+        <v>1373012</v>
       </c>
       <c r="G24" s="15">
-        <v>3156.37</v>
+        <v>3278.07</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0180197651809</v>
+        <v>0.0175433150724</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1779,25 +1770,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F25" s="14">
-        <v>923329</v>
+        <v>26087</v>
       </c>
       <c r="G25" s="15">
-        <v>2993.89</v>
+        <v>3213.28</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0170921643462</v>
+        <v>0.0171965770883</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1817,16 +1808,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="F26" s="14">
-        <v>407725</v>
+        <v>938893</v>
       </c>
       <c r="G26" s="15">
-        <v>2919.31</v>
+        <v>3138.25</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0166663859719</v>
+        <v>0.0167950374843</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1837,25 +1828,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="F27" s="14">
-        <v>1319087</v>
+        <v>414631</v>
       </c>
       <c r="G27" s="15">
-        <v>2906.61</v>
+        <v>2983.06</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0165938814754</v>
+        <v>0.0159645039489</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1878,13 +1869,13 @@
         <v>68</v>
       </c>
       <c r="F28" s="14">
-        <v>81071</v>
+        <v>80693</v>
       </c>
       <c r="G28" s="15">
-        <v>2829.13</v>
+        <v>2867.99</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0161515469562</v>
+        <v>0.0153486814481</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1904,16 +1895,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F29" s="14">
-        <v>885617</v>
+        <v>1628084</v>
       </c>
       <c r="G29" s="15">
-        <v>2673.23</v>
+        <v>2621.22</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0152615114434</v>
+        <v>0.0140280373311</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -1924,25 +1915,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F30" s="14">
-        <v>21861</v>
+        <v>900541</v>
       </c>
       <c r="G30" s="15">
-        <v>2514.74</v>
+        <v>2610.67</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0143566895804</v>
+        <v>0.0139715766778</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -1965,13 +1956,13 @@
         <v>76</v>
       </c>
       <c r="F31" s="14">
-        <v>1601102</v>
+        <v>22701</v>
       </c>
       <c r="G31" s="15">
-        <v>2155.88</v>
+        <v>2541.89</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0123079522864</v>
+        <v>0.0136034853281</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -1991,16 +1982,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F32" s="14">
-        <v>123573</v>
+        <v>107267</v>
       </c>
       <c r="G32" s="15">
-        <v>2069.17</v>
+        <v>2162.29</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0118129235544</v>
+        <v>0.0115719721506</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2020,16 +2011,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="F33" s="14">
-        <v>87592</v>
+        <v>145128</v>
       </c>
       <c r="G33" s="15">
-        <v>2015.54</v>
+        <v>2078.74</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0115067490543</v>
+        <v>0.0111248358862</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2040,25 +2031,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F34" s="14">
-        <v>105477</v>
+        <v>89080</v>
       </c>
       <c r="G34" s="15">
-        <v>1832.29</v>
+        <v>2013.25</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0104605719682</v>
+        <v>0.0107743516976</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2069,25 +2060,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="F35" s="14">
-        <v>69312</v>
+        <v>125717</v>
       </c>
       <c r="G35" s="15">
-        <v>1603.22</v>
+        <v>1978.79</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0091528077929</v>
+        <v>0.0105899314023</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2110,13 +2101,13 @@
         <v>88</v>
       </c>
       <c r="F36" s="14">
-        <v>142709</v>
+        <v>70489</v>
       </c>
       <c r="G36" s="15">
-        <v>1569.23</v>
+        <v>1689.45</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0089587583568</v>
+        <v>0.0090414645352</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2139,13 +2130,13 @@
         <v>17</v>
       </c>
       <c r="F37" s="14">
-        <v>128665</v>
+        <v>129310</v>
       </c>
       <c r="G37" s="15">
-        <v>1276.55</v>
+        <v>1056.59</v>
       </c>
       <c r="H37" s="16">
-        <v>0.007287843707</v>
+        <v>0.0056545745735</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2156,620 +2147,603 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" ht="15" customHeight="1">
+      <c r="B39" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="13" t="s">
+      <c r="H39" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" ht="15" customHeight="1">
+      <c r="B40" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" ht="15" customHeight="1">
+      <c r="B41" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F38" s="14">
-        <v>179874</v>
-      </c>
-      <c r="G38" s="15">
-        <v>296.16</v>
-      </c>
-      <c r="H38" s="16">
-        <v>0.0016907820236</v>
-      </c>
-      <c r="I38" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" ht="15" customHeight="1">
-      <c r="B39" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" ht="15" customHeight="1">
-      <c r="B40" s="7" t="s">
+      <c r="C41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" ht="15" customHeight="1">
+      <c r="B42" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" ht="15" customHeight="1">
+      <c r="B43" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="15" customHeight="1">
+      <c r="B44" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" ht="15" customHeight="1">
+      <c r="B45" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="9" t="s">
+      <c r="C45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="15" customHeight="1">
+      <c r="B46" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15" customHeight="1">
+      <c r="B47" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="H40" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" ht="15" customHeight="1">
-      <c r="B41" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" ht="15" customHeight="1">
-      <c r="B42" s="7" t="s">
+      <c r="C47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" ht="15" customHeight="1">
+      <c r="B48" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="15" customHeight="1">
+      <c r="B49" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" ht="15" customHeight="1">
-      <c r="B43" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" ht="15" customHeight="1">
-      <c r="B44" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J44" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" ht="15" customHeight="1">
-      <c r="B46" s="7" t="s">
+      <c r="C49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="15" customHeight="1">
+      <c r="B50" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" ht="15" customHeight="1">
+      <c r="B51" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" ht="15" customHeight="1">
-      <c r="B48" s="7" t="s">
+      <c r="C51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" ht="15" customHeight="1">
+      <c r="B52" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" ht="15" customHeight="1">
+      <c r="B53" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J48" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" ht="15" customHeight="1">
-      <c r="B49" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="7" t="s">
+      <c r="C53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" ht="15" customHeight="1">
+      <c r="B54" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" ht="15" customHeight="1">
+      <c r="B55" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" ht="15" customHeight="1">
-      <c r="B52" s="7" t="s">
+      <c r="C55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" ht="15" customHeight="1">
+      <c r="B56" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" ht="15" customHeight="1">
+      <c r="B57" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" ht="15" customHeight="1">
-      <c r="B53" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="7" t="s">
+      <c r="C57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" ht="15" customHeight="1">
+      <c r="B58" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="15" customHeight="1">
+      <c r="B59" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" ht="15" customHeight="1">
-      <c r="B55" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" ht="15" customHeight="1">
-      <c r="B56" s="7" t="s">
+      <c r="C59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" ht="15" customHeight="1">
+      <c r="B60" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" ht="15" customHeight="1">
+      <c r="B61" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H56" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" ht="15" customHeight="1">
-      <c r="B57" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" ht="15" customHeight="1">
-      <c r="B58" s="7" t="s">
+      <c r="C61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" ht="15" customHeight="1">
+      <c r="B62" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" ht="15" customHeight="1">
+      <c r="B63" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" ht="15" customHeight="1">
-      <c r="B59" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J59" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" ht="15" customHeight="1">
-      <c r="B60" s="7" t="s">
+      <c r="C63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="15" customHeight="1">
+      <c r="B64" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" ht="15" customHeight="1">
+      <c r="B65" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C60" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H60" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J60" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" ht="15" customHeight="1">
-      <c r="B61" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" ht="15" customHeight="1">
-      <c r="B62" s="7" t="s">
+      <c r="C65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="9">
+        <v>247.09</v>
+      </c>
+      <c r="H65" s="10">
+        <v>0.0013223566675</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="15" customHeight="1">
+      <c r="B66" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" ht="15" customHeight="1">
+      <c r="B67" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C62" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10" ht="15" customHeight="1">
-      <c r="B63" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" ht="15" customHeight="1">
-      <c r="B64" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H64" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J64" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" ht="15" customHeight="1">
-      <c r="B65" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" ht="15" customHeight="1">
-      <c r="B66" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="9">
-        <v>160.36</v>
-      </c>
-      <c r="H66" s="10">
-        <v>0.0009154977218</v>
-      </c>
-      <c r="I66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" ht="15" customHeight="1">
-      <c r="B67" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J67" s="11" t="s">
+      <c r="C67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="18">
+        <v>34.110166200000094</v>
+      </c>
+      <c r="H67" s="19">
+        <v>0.0001825480825060899</v>
+      </c>
+      <c r="I67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="18">
+        <v>186855.7901662</v>
+      </c>
+      <c r="H68" s="19">
+        <v>0.9999999999984063</v>
+      </c>
+      <c r="I68" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J68" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" ht="15" customHeight="1">
+      <c r="B71" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+    </row>
+    <row r="72" spans="2:8" ht="15" customHeight="1">
+      <c r="B72" s="13" t="s">
         <v>108</v>
-      </c>
-      <c r="C68" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="18">
-        <v>-53.37998489005258</v>
-      </c>
-      <c r="H68" s="19">
-        <v>-0.0003047471598958096</v>
-      </c>
-      <c r="I68" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J68" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" ht="15" customHeight="1">
-      <c r="B69" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" s="18">
-        <v>175161.55001511</v>
-      </c>
-      <c r="H69" s="19">
-        <v>0.9999999999985043</v>
-      </c>
-      <c r="I69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J69" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9" ht="15" customHeight="1">
-      <c r="B72" s="13" t="s">
-        <v>110</v>
       </c>
       <c r="C72" s="21"/>
       <c r="D72" s="21"/>
@@ -2777,11 +2751,10 @@
       <c r="F72" s="21"/>
       <c r="G72" s="21"/>
       <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-    </row>
-    <row r="73" spans="2:8" ht="15" customHeight="1">
-      <c r="B73" s="13" t="s">
-        <v>111</v>
+    </row>
+    <row r="73" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B73" s="22" t="s">
+        <v>109</v>
       </c>
       <c r="C73" s="21"/>
       <c r="D73" s="21"/>
@@ -2792,7 +2765,7 @@
     </row>
     <row r="74" spans="2:8" ht="27.6" customHeight="1">
       <c r="B74" s="22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C74" s="21"/>
       <c r="D74" s="21"/>
@@ -2803,7 +2776,7 @@
     </row>
     <row r="75" spans="2:8" ht="27.6" customHeight="1">
       <c r="B75" s="22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
@@ -2812,42 +2785,31 @@
       <c r="G75" s="21"/>
       <c r="H75" s="21"/>
     </row>
-    <row r="76" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B76" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-    </row>
-    <row r="79" ht="15">
-      <c r="B79" s="21" t="s">
-        <v>115</v>
+    <row r="78" ht="15">
+      <c r="B78" s="21" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="93" ht="15">
+      <c r="B93" s="21" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="94" ht="15">
       <c r="B94" s="21" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="95" ht="15">
-      <c r="B95" s="21" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B73:H73"/>
     <mergeCell ref="B74:H74"/>
     <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B76:H76"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B73:H73"/>
+    <mergeCell ref="B71:I71"/>
+    <mergeCell ref="B72:H72"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
